--- a/reports/一级子公司B_利润表_2026-05.xlsx
+++ b/reports/一级子公司B_利润表_2026-05.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>50702182</v>
+        <v>67479288</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>15093221</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>70171340</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>210972</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>985962</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>190118</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>886549</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>158759</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>738333</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>148542</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>688966</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>85089</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>393788</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>63944</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>295531</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>50702182</v>
+        <v>66621864</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>14235797</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>8530341</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>39522408</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1277317</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>5932899</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>637169</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>2967621</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>4237122</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>19783278</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>422759</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>1977388</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>316566</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>1481820</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>527271</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>2467165</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>421993</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>1971660</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>50619757</v>
+        <v>50710242</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>236583079</v>
+        <v>236388736</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>82425</v>
+        <v>82231</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>412441</v>
+        <v>411084</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>955234</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>4429093</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>638360</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>2953600</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>52293115</v>
+        <v>66377554</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>26543090</v>
+        <v>34335800</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>159732</v>
+        <v>7683453</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>739906</v>
+        <v>35539583</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>26383358</v>
+        <v>26652347</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>123189332</v>
+        <v>123522209</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1596191</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>7416688</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>509565</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2374145</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>317681</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1483688</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>380385</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1779485</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>284868</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1333467</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>189816</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>888052</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>158268</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>739274</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1268001</v>
+        <v>1268072</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>5921241</v>
+        <v>5909143</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>42652</v>
+        <v>42363</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>197597</v>
+        <v>196869</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2658298</v>
+        <v>2654318</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>12327351</v>
+        <v>12303204</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>21357464</v>
+        <v>21550923</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>79463143</v>
+        <v>79432545</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2665427</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>12316584</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>466262</v>
+        <v>466240</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2319372</v>
+        <v>2315817</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>411305</v>
+        <v>414395</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2057434</v>
+        <v>2060653</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>30733</v>
+        <v>31045</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>154439</v>
+        <v>154702</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>139432</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>696684</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>278575</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1298376</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>92499</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>464621</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>69228</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>348306</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>115223</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>580040</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>395456</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1849846</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>61473</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>308724</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>46180</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>231340</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>77142</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>385349</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>54135</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>269701</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>38758</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>192699</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>31059</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>154263</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>23313</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>115806</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>-1590933</v>
+        <v>1211623</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-119959</v>
+        <v>4749032</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>159524</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>741767</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>38624</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>193603</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>61452</v>
+        <v>61647</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>308838</v>
+        <v>309736</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>-1652385</v>
+        <v>1309500</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1862597</v>
+        <v>1843371</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>9270657</v>
+        <v>9279483</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>-3514982</v>
+        <v>-533871</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>-3514982</v>
+        <v>-533871</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>-3514982</v>
+        <v>-533871</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>-3514982</v>
+        <v>-533871</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>-3514982</v>
+        <v>-533871</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
